--- a/trade_history.xlsx
+++ b/trade_history.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -680,6 +680,27 @@
         <v>9</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-2506</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-0.00835</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -691,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4718,6 +4739,439 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>商社・卸売</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>★ LONG</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>4919</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>4863</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>-0.01138</v>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>-683</v>
+      </c>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K84" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1631.T</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>★ LONG</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>37380</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>37140</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>-0.00642</v>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>-385</v>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K85" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1618.T</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>エネルギー資源</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>★ LONG</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>34200</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>33910</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>-0.00848</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>-509</v>
+      </c>
+      <c r="J86" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1623.T</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>鉄鋼・非鉄</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>★ LONG</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>70400</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>-0.008449999999999999</v>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>-507</v>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1624.T</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>★ LONG</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>価格異常</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1628.T</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>運輸・物流</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>▼ SHORT</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>20330</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>20480</v>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>0.00738</v>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>-443</v>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K89" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>1621.T</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>医薬品</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>▼ SHORT</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>28485</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>28565</v>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>0.00281</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>-169</v>
+      </c>
+      <c r="J90" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K90" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>1627.T</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>電力・ガス</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>▼ SHORT</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>11345</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>11365</v>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>0.00176</v>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>-106</v>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K91" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>1630.T</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>小売</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>▼ SHORT</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>36470</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>36290</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>-0.00494</v>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>296</v>
+      </c>
+      <c r="J92" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
